--- a/DataTables/DetailText/剧情/026_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/026_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A01A3A-5783-42F9-B68D-E91EA15677D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5CC6E5-48BF-41DD-87F6-9B43702F5626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -141,10 +130,6 @@
   </si>
   <si>
     <t>story_npc_cured</t>
-  </si>
-  <si>
-    <t>023治疗成功</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>半夏</t>
@@ -337,16 +322,42 @@
     <t>026_01</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <r>
+      <t>026治</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成功</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -360,7 +371,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -381,7 +392,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -405,6 +416,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -523,7 +541,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -802,27 +820,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -872,12 +890,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -891,7 +909,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -906,66 +924,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="14"/>
       <c r="L3" s="18"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="C8" s="10"/>
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8" ht="18.75">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -977,20 +995,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1016,7 +1034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1024,7 +1042,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -1032,13 +1050,13 @@
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1046,7 +1064,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -1055,10 +1073,10 @@
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1066,7 +1084,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>9</v>
@@ -1075,10 +1093,10 @@
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1086,7 +1104,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
@@ -1095,10 +1113,10 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1106,7 +1124,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -1115,10 +1133,10 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1130,7 +1148,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1142,7 +1160,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1154,7 +1172,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1166,7 +1184,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>

--- a/DataTables/DetailText/剧情/026_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/026_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5CC6E5-48BF-41DD-87F6-9B43702F5626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C29085-5047-49B3-80D3-938317329F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20490" yWindow="4125" windowWidth="18900" windowHeight="10905" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -137,10 +148,6 @@
   </si>
   <si>
     <t>res://Assets/Background/023/023.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>呜呜呜，夫人到底是得了什么病啊。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -345,6 +352,29 @@
         <charset val="134"/>
       </rPr>
       <t>成功</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>呜呜呜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，少夫人到底是得了什么病啊。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -357,7 +387,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -371,7 +401,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -392,7 +422,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -541,7 +571,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -820,24 +850,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -892,10 +922,10 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -909,7 +939,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -930,60 +960,60 @@
       <c r="L3" s="18"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16">
       <c r="C8" s="10"/>
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" ht="18.75">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -997,14 +1027,14 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1044,16 +1074,16 @@
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
+      <c r="D2" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>32</v>
+      <c r="H2" s="19" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1064,16 +1094,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1084,7 +1114,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>9</v>
@@ -1093,7 +1123,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1104,16 +1134,16 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1126,14 +1156,14 @@
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
+      <c r="D6" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/026_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/026_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C29085-5047-49B3-80D3-938317329F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281F236F-CA70-4382-8D9D-EFB02CF736B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20490" yWindow="4125" windowWidth="18900" windowHeight="10905" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>LineIndex</t>
   </si>
@@ -84,63 +70,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
     <t>clinic</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>story_npc_cured</t>
   </si>
   <si>
     <t>半夏</t>
@@ -378,16 +314,104 @@
     </r>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>cured</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -401,7 +425,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -422,20 +446,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -456,8 +472,30 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -472,20 +510,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -516,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -542,24 +582,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -569,9 +598,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -849,175 +906,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="22" customFormat="1">
+      <c r="A1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="S1" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="22" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="15" t="s">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="K2" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="23"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="C3" s="10"/>
-      <c r="H3" s="14"/>
-      <c r="L3" s="18"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="C4" s="10"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="C5" s="10"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="C6" s="10"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="C7" s="10"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="C8" s="10"/>
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="H16" s="14"/>
+      <c r="T2" s="24"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="L3" s="13"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="9"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="9"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="9"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="9"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="C8" s="9"/>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="11"/>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="14"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="14"/>
+      <c r="H18" s="11"/>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="14"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="14"/>
+      <c r="H20" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{49C735F3-F8E1-436D-B7A0-D92F39057ADA}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{6DC8FF34-A7A2-4612-BF1B-1384D0DE1C95}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{AD69280A-7E1B-45D0-96D0-6A16602B9EE5}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{52B6F0AB-0118-4D83-9B25-036D71BC62DD}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{3A5EC35A-F239-40EB-9D99-B2D945086B78}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1027,41 +1113,41 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1069,21 +1155,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1091,19 +1177,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1111,19 +1197,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1131,19 +1217,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="19" t="s">
-        <v>36</v>
+      <c r="H5" s="14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1151,19 +1237,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/026_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/026_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281F236F-CA70-4382-8D9D-EFB02CF736B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BE9176-96C5-471A-BE99-F16B9C000257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>LineIndex</t>
   </si>
@@ -74,9 +85,6 @@
   </si>
   <si>
     <t>SortIndex</t>
-  </si>
-  <si>
-    <t>clinic</t>
   </si>
   <si>
     <t>半夏</t>
@@ -401,6 +409,9 @@
   </si>
   <si>
     <t>cured</t>
+  </si>
+  <si>
+    <t>night</t>
   </si>
 </sst>
 </file>
@@ -411,7 +422,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -425,7 +436,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -446,7 +457,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -628,7 +639,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -907,78 +918,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1">
+    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="J1" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="K1" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="L1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>43</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>44</v>
       </c>
       <c r="S1" s="21" t="s">
         <v>12</v>
@@ -987,16 +998,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="22" customFormat="1">
+    <row r="2" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>14</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C2" s="14"/>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
       <c r="F2" s="14"/>
@@ -1004,13 +1013,13 @@
       <c r="H2" s="14"/>
       <c r="I2" s="23"/>
       <c r="J2" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" s="14" t="s">
         <v>45</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>14</v>
       </c>
       <c r="M2" s="23"/>
       <c r="N2" s="14"/>
@@ -1113,14 +1122,14 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1158,7 +1167,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>7</v>
@@ -1166,10 +1175,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1180,7 +1189,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -1189,7 +1198,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1200,7 +1209,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>8</v>
@@ -1209,7 +1218,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1220,7 +1229,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -1229,7 +1238,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1240,7 +1249,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>7</v>
@@ -1249,7 +1258,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/026_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/026_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BE9176-96C5-471A-BE99-F16B9C000257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5930A856-3048-498E-9FC4-4AEC6EC53E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19395" yWindow="5745" windowWidth="16050" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
   <si>
     <t>LineIndex</t>
   </si>
@@ -412,6 +412,10 @@
   </si>
   <si>
     <t>night</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="10"/>
   </si>
 </sst>
 </file>
@@ -567,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -636,6 +640,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1119,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -1129,11 +1136,11 @@
     <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="56.75" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1158,8 +1165,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1180,8 +1190,9 @@
       <c r="H2" s="14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1200,8 +1211,9 @@
       <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1220,8 +1232,9 @@
       <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1240,8 +1253,9 @@
       <c r="H5" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1260,8 +1274,9 @@
       <c r="H6" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1272,8 +1287,9 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1284,8 +1300,9 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1296,8 +1313,9 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1308,8 +1326,9 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1320,6 +1339,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/026_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/026_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5930A856-3048-498E-9FC4-4AEC6EC53E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA82CC74-4EF5-438C-B845-4B5BC322775C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19395" yWindow="5745" windowWidth="16050" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -91,10 +91,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Background/023/023.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>李东璧</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -416,6 +412,10 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/026/026.png</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -426,7 +426,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -440,7 +440,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -461,7 +461,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -646,7 +646,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -925,78 +925,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="22" customFormat="1">
       <c r="A1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="J1" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="K1" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="L1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>42</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>43</v>
       </c>
       <c r="S1" s="21" t="s">
         <v>12</v>
@@ -1005,12 +1005,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="22" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="22" customFormat="1">
       <c r="A2" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
@@ -1020,13 +1020,13 @@
       <c r="H2" s="14"/>
       <c r="I2" s="23"/>
       <c r="J2" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="14" t="s">
         <v>44</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>45</v>
       </c>
       <c r="M2" s="23"/>
       <c r="N2" s="14"/>
@@ -1129,14 +1129,14 @@
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="56.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.73046875" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1166,7 +1166,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1185,10 +1185,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1200,7 +1200,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -1209,7 +1209,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1221,7 +1221,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>8</v>
@@ -1230,7 +1230,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1242,7 +1242,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -1251,7 +1251,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1272,7 +1272,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6" s="1"/>
     </row>
